--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.55856628913639</v>
+        <v>3.990767021984663</v>
       </c>
       <c r="D2" t="n">
-        <v>24.3913606475877</v>
+        <v>3.963596105233001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.907068613032902</v>
+        <v>1.284898649617846</v>
       </c>
       <c r="F2" t="n">
-        <v>7.976810755507771</v>
+        <v>1.296231747770013</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.02998898822055</v>
+        <v>1.62987321058584</v>
       </c>
       <c r="D3" t="n">
-        <v>9.945826395553047</v>
+        <v>1.61619678927737</v>
       </c>
       <c r="E3" t="n">
-        <v>7.907068613032902</v>
+        <v>1.284898649617846</v>
       </c>
       <c r="F3" t="n">
-        <v>7.976810755507771</v>
+        <v>1.296231747770013</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.661632030816</v>
+        <v>3.5200152050076</v>
       </c>
       <c r="D4" t="n">
-        <v>21.73475393295151</v>
+        <v>3.53189751410462</v>
       </c>
       <c r="E4" t="n">
-        <v>7.907068613032902</v>
+        <v>1.284898649617846</v>
       </c>
       <c r="F4" t="n">
-        <v>7.976810755507771</v>
+        <v>1.296231747770013</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.55423817211978</v>
+        <v>3.177563702969464</v>
       </c>
       <c r="D5" t="n">
-        <v>19.55384411258195</v>
+        <v>3.177499668294566</v>
       </c>
       <c r="E5" t="n">
-        <v>7.907068613032902</v>
+        <v>1.284898649617846</v>
       </c>
       <c r="F5" t="n">
-        <v>7.976810755507771</v>
+        <v>1.296231747770013</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.57108385826407</v>
+        <v>4.642801126967912</v>
       </c>
       <c r="D6" t="n">
-        <v>28.53781442033264</v>
+        <v>4.637394843304054</v>
       </c>
       <c r="E6" t="n">
-        <v>7.907068613032902</v>
+        <v>1.284898649617846</v>
       </c>
       <c r="F6" t="n">
-        <v>7.976810755507771</v>
+        <v>1.296231747770013</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14.24440437504877</v>
+        <v>2.314715710945426</v>
       </c>
       <c r="D7" t="n">
-        <v>14.38647453140854</v>
+        <v>2.337802111353888</v>
       </c>
       <c r="E7" t="n">
-        <v>7.907068613032902</v>
+        <v>1.284898649617846</v>
       </c>
       <c r="F7" t="n">
-        <v>7.976810755507771</v>
+        <v>1.296231747770013</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.54848757742537</v>
+        <v>4.314129231331622</v>
       </c>
       <c r="D8" t="n">
-        <v>26.72222380833096</v>
+        <v>4.342361368853782</v>
       </c>
       <c r="E8" t="n">
-        <v>7.907068613032902</v>
+        <v>1.284898649617846</v>
       </c>
       <c r="F8" t="n">
-        <v>7.976810755507771</v>
+        <v>1.296231747770013</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.68006989307577</v>
+        <v>5.148011357624814</v>
       </c>
       <c r="D9" t="n">
-        <v>31.79796262192979</v>
+        <v>5.16716892606359</v>
       </c>
       <c r="E9" t="n">
-        <v>7.907068613032902</v>
+        <v>1.284898649617846</v>
       </c>
       <c r="F9" t="n">
-        <v>7.976810755507771</v>
+        <v>1.296231747770013</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>29.12552309267992</v>
+        <v>4.732897502560487</v>
       </c>
       <c r="D10" t="n">
-        <v>29.28007975445039</v>
+        <v>4.758012960098188</v>
       </c>
       <c r="E10" t="n">
-        <v>7.907068613032902</v>
+        <v>1.284898649617846</v>
       </c>
       <c r="F10" t="n">
-        <v>7.976810755507771</v>
+        <v>1.296231747770013</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>7.688607511827689</v>
+        <v>1.249398720671999</v>
       </c>
       <c r="D11" t="n">
-        <v>7.473254405675031</v>
+        <v>1.214403840922193</v>
       </c>
       <c r="E11" t="n">
-        <v>7.907068613032902</v>
+        <v>1.284898649617846</v>
       </c>
       <c r="F11" t="n">
-        <v>7.976810755507771</v>
+        <v>1.296231747770013</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
